--- a/artfynd/A 19158-2023 artfynd.xlsx
+++ b/artfynd/A 19158-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>116362285</v>
       </c>
       <c r="B2" t="n">
-        <v>97758</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,7 +710,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjältern (Mjältern), Sm</t>
+          <t>Mjältern, Mjältern, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116362884</v>
+        <v>116361802</v>
       </c>
       <c r="B3" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,17 +807,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjältern (Mjältern), Sm</t>
+          <t>Mjältern, Mjältern, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550599</v>
+        <v>550593</v>
       </c>
       <c r="R3" t="n">
-        <v>6378583</v>
+        <v>6378708</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -836,7 +826,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Vimmerby</t>
+          <t>Hultsfred</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -846,7 +836,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Vimmerby</t>
+          <t>Vena</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -886,12 +876,7 @@
         <v>116361997</v>
       </c>
       <c r="B4" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,7 +904,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjältern (Mjältern), Sm</t>
+          <t>Mjältern, Mjältern, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -982,6 +967,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116362884</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mjältern, Mjältern, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550599</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6378583</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19158-2023 artfynd.xlsx
+++ b/artfynd/A 19158-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116362285</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116361802</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116361997</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,8 +1084,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116362884</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>